--- a/working-example/DGF-temporal-demo.xlsx
+++ b/working-example/DGF-temporal-demo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -29,55 +29,46 @@
     <t xml:space="preserve">dd_f_levels</t>
   </si>
   <si>
+    <t xml:space="preserve">dd_is_join_key</t>
+  </si>
+  <si>
     <t xml:space="preserve">raw_data_storage</t>
   </si>
   <si>
-    <t xml:space="preserve">raw_data_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_data_subtype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_data_class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_data_unit</t>
-  </si>
-  <si>
     <t xml:space="preserve">raw_data_format</t>
   </si>
   <si>
-    <t xml:space="preserve">raw_data_import_rule</t>
-  </si>
-  <si>
     <t xml:space="preserve">raw_first5</t>
   </si>
   <si>
     <t xml:space="preserve">raw_duplicated</t>
   </si>
   <si>
+    <t xml:space="preserve">raw_to_stable_transform</t>
+  </si>
+  <si>
     <t xml:space="preserve">stable_data_storage</t>
   </si>
   <si>
-    <t xml:space="preserve">stable_data_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stable_data_subtype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stable_data_class</t>
-  </si>
-  <si>
     <t xml:space="preserve">stable_data_unit</t>
   </si>
   <si>
     <t xml:space="preserve">stable_data_format</t>
   </si>
   <si>
-    <t xml:space="preserve">stable_data_transform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stable_data_import_rule</t>
+    <t xml:space="preserve">desired_data_import_rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desired_data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desired_data_subtype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desired_data_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desired_data_format</t>
   </si>
   <si>
     <t xml:space="preserve">rg_properties</t>
@@ -114,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">numeric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number</t>
   </si>
   <si>
     <t xml:space="preserve">190102000 ;; 
@@ -188,14 +176,14 @@
     <t xml:space="preserve">character</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">Organization B 985 ;; 
 Organization W 652 ;; 
 Organization H 831 ;; 
 Organization T 342 ;; 
 Organization C 116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
   </si>
   <si>
     <t xml:space="preserve">Organization A 158 ;; Organization A 202 ;; Organization A 276 ;; Organization A 279 ;; Organization A 412 ;; Organization A 530 ;; Organization A 589 ;; Organization A 604 ;; Organization A 605 ;; Organization A 657 ;; Organization A 735 ;; Organization A 74 ;; Organization A 780 ;; Organization A 916 ;; Organization A 935 ;; Organization A 954 ;; Organization A 962 ;; Organization B 252 ;; Organ</t>
@@ -457,11 +445,11 @@
     <t xml:space="preserve">logical</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRUE ;; 
 FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -509,10 +497,10 @@
 SAT</t>
   </si>
   <si>
+    <t xml:space="preserve">dow</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dow</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -1272,9 +1260,6 @@
     <t xml:space="preserve">hms</t>
   </si>
   <si>
-    <t xml:space="preserve">unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">02:38:00 ;; 
 19:05:00 ;; 
 05:51:00 ;; 
@@ -1286,6 +1271,15 @@
   </si>
   <si>
     <t xml:space="preserve">hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time_of_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hhii</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -2497,9 +2491,6 @@
     <col min="26" max="26" width="20.71" hidden="0" customWidth="1"/>
     <col min="27" max="27" width="20.71" hidden="0" customWidth="1"/>
     <col min="28" max="28" width="20.71" hidden="0" customWidth="1"/>
-    <col min="29" max="29" width="20.71" hidden="0" customWidth="1"/>
-    <col min="30" max="30" width="20.71" hidden="0" customWidth="1"/>
-    <col min="31" max="31" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -2587,1344 +2578,1209 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="J2" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="Q2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="U2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="V2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="8" t="s">
+      <c r="W2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="V3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="W3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="X3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="N3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA3" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="Q4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="U4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="s">
+      <c r="V4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="W4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W4" s="7" t="s">
+      <c r="X4" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE4" s="7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="V5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="11" t="s">
+      <c r="W5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W5" s="7" t="s">
+      <c r="X5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="X5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="Q6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="U6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="V6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="11" t="s">
+      <c r="W6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="N6" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W6" s="7" t="s">
+      <c r="X6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB6" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="X6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="Q7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="U7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P7" s="8" t="s">
+      <c r="V7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" s="6" t="s">
+      <c r="X7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB7" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="X7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="U8" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="11" t="s">
+      <c r="V8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W8" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="N8" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="6" t="s">
+      <c r="X8" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB8" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="X8" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z8" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA8" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB9" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="N9" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="X9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE9" s="7" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="U10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="11" t="s">
+      <c r="V10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="N10" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="6" t="s">
+      <c r="X10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB10" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="X10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE10" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="11" t="s">
+      <c r="X11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB11" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="N11" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="X11" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE11" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="N12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="R12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="11" t="s">
+      <c r="S12" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="N12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" s="8" t="s">
+      <c r="T12" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="P12" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S12" s="6" t="s">
+      <c r="U12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U12" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="V12" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W12" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X12" s="7" t="s">
+      <c r="X12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB12" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="Y12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE12" s="7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="11" t="s">
+      <c r="N13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="U13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="N13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S13" s="6" t="s">
+      <c r="V13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="T13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="X13" s="7" t="s">
+      <c r="X13" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="Y13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z13" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="AA13" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" s="11" t="s">
+      <c r="N14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T14" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="N14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S14" s="6" t="s">
+      <c r="U14" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="T14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U14" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="V14" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W14" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="X14" s="7" t="s">
+      <c r="X14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB14" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="Y14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z14" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE14" s="7" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="U15" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" s="11" t="s">
+      <c r="V15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="W15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="N15" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="X15" s="7" t="s">
+      <c r="X15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB15" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="Y15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE15" s="7" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/working-example/DGF-temporal-demo.xlsx
+++ b/working-example/DGF-temporal-demo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -104,7 +104,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">numeric</t>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">character</t>
   </si>
   <si>
     <t xml:space="preserve">190102000 ;; 
@@ -114,7 +117,19 @@
 389542352</t>
   </si>
   <si>
+    <t xml:space="preserve">numeric</t>
+  </si>
+  <si>
     <t xml:space="preserve">identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">administrative_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -171,9 +186,6 @@
   </si>
   <si>
     <t xml:space="preserve">org_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">character</t>
   </si>
   <si>
     <t xml:space="preserve">Organization B 985 ;; 
@@ -439,10 +451,9 @@
   </si>
   <si>
     <t xml:space="preserve">[ 
+  {  "level" :  "FALSE"  ,  "label" :  "FALSE"  }, 
+  {  "level" :  "TRUE"  ,  "label" :  "TRUE"  }
 ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logical</t>
   </si>
   <si>
     <t xml:space="preserve">TRUE ;; 
@@ -473,7 +484,7 @@
 ]</t>
   </si>
   <si>
-    <t xml:space="preserve">603ad2c21b1d7fe0d94ee1bbc2e1384b</t>
+    <t xml:space="preserve">d36d673f7b22edc905d9d8b9aa91609b</t>
   </si>
   <si>
     <t xml:space="preserve">day_of_week</t>
@@ -1257,17 +1268,11 @@
     <t xml:space="preserve">hour_ampm</t>
   </si>
   <si>
-    <t xml:space="preserve">hms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:38:00 ;; 
-19:05:00 ;; 
-05:51:00 ;; 
-05:27:00 ;; 
-08:07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c("hms", "difftime")</t>
+    <t xml:space="preserve">2:38am ;; 
+7:05pm ;; 
+5:51am ;; 
+5:27am ;; 
+8:07am</t>
   </si>
   <si>
     <t xml:space="preserve">hour</t>
@@ -1288,282 +1293,282 @@
 ]</t>
   </si>
   <si>
-    <t xml:space="preserve">00:36:00 ;; 01:51:00 ;; 02:16:00 ;; 02:32:00 ;; 02:38:00 ;; 02:55:00 ;; 04:09:00 ;; 04:18:00 ;; 04:52:00 ;; 05:07:00 ;; 05:59:00 ;; 07:06:00 ;; 07:39:00 ;; 08:08:00 ;; 08:15:00 ;; 08:22:00 ;; 09:52:00 ;; 10:26:00 ;; 13:27:00 ;; 14:26:00 ;; 14:48:00 ;; 15:02:00 ;; 15:12:00 ;; 15:26:00 ;; 15:36:00 ;; 15:42:00 ;; 17:18:00 ;; 19:05:00 ;; 20:19:00 ;; 21:55:00 ;; 22:27:00 ;; 22:48:00 ;; 00:02:00 ;; 00:0</t>
+    <t xml:space="preserve">1:27pm ;; 1:51am ;; 10:26am ;; 10:27pm ;; 10:48pm ;; 12:36am ;; 2:16am ;; 2:26pm ;; 2:32am ;; 2:38am ;; 2:48pm ;; 2:55am ;; 3:02pm ;; 3:12pm ;; 3:26pm ;; 3:36pm ;; 3:42pm ;; 4:09am ;; 4:18am ;; 4:52am ;; 5:07am ;; 5:18pm ;; 5:59am ;; 7:05pm ;; 7:06am ;; 7:39am ;; 8:08am ;; 8:15am ;; 8:19pm ;; 8:22am ;; 9:52am ;; 9:55pm ;; 1:00am ;; 1:02am ;; 1:04am ;; 1:10am ;; 1:10pm ;; 1:11am ;; 1:15pm ;; 1:16pm</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
-  {  "Value" :  "00 :  02 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  07 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  12 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  13 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  23 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  24 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  36 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "00 :  38 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  41 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  51 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "00 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  00 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  02 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  04 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  10 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  11 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  36 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  39 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  41 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "01 :  51 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "01 :  52 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  02 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  03 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  04 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  11 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  14 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  16 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "02 :  25 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  26 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  27 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  32 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "02 :  38 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "02 :  41 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "02 :  55 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "03 :  10 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  19 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  26 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  28 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  36 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  38 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  46 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  50 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  54 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "03 :  55 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  09 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "04 :  13 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  18 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "04 :  20 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  52 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "04 :  55 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "04 :  59 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  00 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  07 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "05 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  19 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  27 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  35 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  50 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  51 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  57 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "05 :  59 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "06 :  02 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  13 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  25 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  43 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  52 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "06 :  54 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  06 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "07 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  19 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  21 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  39 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "07 :  47 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  52 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "07 :  54 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  05 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  07 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  08 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "08 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  15 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "08 :  22 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "08 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  40 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "08 :  52 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  06 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  36 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  45 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  48 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "09 :  52 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "09 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  12 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  13 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  19 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  25 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  26 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "10 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "10 :  45 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  17 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "11 :  43 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  06 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  19 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  23 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  35 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  39 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  55 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "12 :  57 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  10 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  20 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  24 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  27 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "13 :  30 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  36 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  43 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "13 :  59 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  06 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  07 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  13 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  17 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  26 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "14 :  30 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  48 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "14 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "14 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  02 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "15 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  12 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "15 :  26 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "15 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  36 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "15 :  39 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  42 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "15 :  47 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  54 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "15 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  07 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  08 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  23 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  30 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  41 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  43 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  44 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  45 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "16 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "17 :  02 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "17 :  10 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "17 :  18 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "17 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "17 :  32 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "17 :  50 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  01 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  05 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  20 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  30 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "18 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  04 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  05 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "19 :  15 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  23 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  25 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  34 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  41 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "19 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  00 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  01 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  14 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  19 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "20 :  21 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  30 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  44 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  46 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  49 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  57 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "20 :  58 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  08 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  09 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  16 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  36 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  38 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  43 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  50 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  52 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "21 :  55 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "21 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  05 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  17 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  26 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  27 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "22 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  34 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  42 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  48 :  00"  ,  "Count" :  2  }, 
-  {  "Value" :  "22 :  50 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  51 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  56 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  57 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "22 :  59 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  00 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  07 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  18 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  21 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  22 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  26 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  29 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  33 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  35 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  37 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  44 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  46 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  47 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  53 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  54 :  00"  ,  "Count" :  1  }, 
-  {  "Value" :  "23 :  59 :  00"  ,  "Count" :  1  }
+  {  "Value" :  "1 :  00am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  02am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  04am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  10am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  10pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  11am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  15pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  16pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  20pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  24pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  27pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "1 :  29am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  30pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  32am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  32pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  33am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  36am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  36pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  37pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  39am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  41am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  42am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  42pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  43pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  49pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  51am"  ,  "Count" :  2  }, 
+  {  "Value" :  "1 :  52am"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  56pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "1 :  59pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  05pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  12am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  13am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  17pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  18am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  19am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  22am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  25am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  26am"  ,  "Count" :  2  }, 
+  {  "Value" :  "10 :  26pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  27pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "10 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  34pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  37am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  42pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  45am"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  48pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "10 :  50pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  51pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  56pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  57pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "10 :  59pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  00pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  07pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  09am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  17am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  18am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  18pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  21pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  22pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  26pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  29pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  32am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  33am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  35pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  37am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  37pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  43am"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  44pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  46pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  47pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  54pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "11 :  59pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  02am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  06pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  07am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  12am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  13am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  19pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  22am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  23am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  23pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  24am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  29am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  29pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  35pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  36am"  ,  "Count" :  2  }, 
+  {  "Value" :  "12 :  38am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  39pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  41am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  49pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  51am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  53am"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  55pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "12 :  57pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  02am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  03am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  04am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  06pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  07pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  11am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  13pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  14am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  15pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  16am"  ,  "Count" :  2  }, 
+  {  "Value" :  "2 :  17pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  22pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  25am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  26am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  26pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "2 :  27am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  30pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  32am"  ,  "Count" :  2  }, 
+  {  "Value" :  "2 :  32pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  38am"  ,  "Count" :  2  }, 
+  {  "Value" :  "2 :  41am"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  48pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "2 :  49pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "2 :  55am"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  02pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  09pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  10am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  12pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  18am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  19am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  26am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  26pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  28am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  32am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  32pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  36am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  36pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  38am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  39pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  42pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "3 :  46am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  47pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  50am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  54am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  54pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  55am"  ,  "Count" :  1  }, 
+  {  "Value" :  "3 :  56pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  07pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  08pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  09am"  ,  "Count" :  2  }, 
+  {  "Value" :  "4 :  13am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  15pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  16am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  18am"  ,  "Count" :  2  }, 
+  {  "Value" :  "4 :  20am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  23pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  30pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  32pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  41pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  42am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  43pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  44pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  45pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  52am"  ,  "Count" :  2  }, 
+  {  "Value" :  "4 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  55am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  56am"  ,  "Count" :  1  }, 
+  {  "Value" :  "4 :  59am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  00am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  02pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  07am"  ,  "Count" :  2  }, 
+  {  "Value" :  "5 :  10pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  15am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  16am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  18pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "5 :  19am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  22pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  27am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  32pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  35am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  37am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  50am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  50pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  51am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  53am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  57am"  ,  "Count" :  1  }, 
+  {  "Value" :  "5 :  59am"  ,  "Count" :  2  }, 
+  {  "Value" :  "6 :  01pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  02am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  05pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  09am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  13am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  18am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  20pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  25am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  29am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  30pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  33pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  37pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  43am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  52am"  ,  "Count" :  1  }, 
+  {  "Value" :  "6 :  54am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  04pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  05pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "7 :  06am"  ,  "Count" :  2  }, 
+  {  "Value" :  "7 :  09am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  15pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  16am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  16pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  19am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  21am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  23pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  25pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  29pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  34pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  39am"  ,  "Count" :  2  }, 
+  {  "Value" :  "7 :  41pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  47am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  49pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  52am"  ,  "Count" :  1  }, 
+  {  "Value" :  "7 :  54am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  00pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  01pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  05am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  07am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  08am"  ,  "Count" :  2  }, 
+  {  "Value" :  "8 :  09am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  09pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  14pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  15am"  ,  "Count" :  2  }, 
+  {  "Value" :  "8 :  18pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  19pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "8 :  21pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  22am"  ,  "Count" :  2  }, 
+  {  "Value" :  "8 :  30pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  32am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  40am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  42pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  44pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  46pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  49am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  49pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  52am"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  57pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "8 :  58pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  06am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  08pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  09pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  15am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  16pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  22pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  36am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  36pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  38pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  42pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  43pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  45am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  48am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  49am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  50pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  52am"  ,  "Count" :  2  }, 
+  {  "Value" :  "9 :  52pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  53pm"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  55pm"  ,  "Count" :  2  }, 
+  {  "Value" :  "9 :  56am"  ,  "Count" :  1  }, 
+  {  "Value" :  "9 :  56pm"  ,  "Count" :  1  }
 ]</t>
   </si>
   <si>
-    <t xml:space="preserve">f88066944d0869466e92833c25c4afc1</t>
+    <t xml:space="preserve">d68259e0179753107e60f9b9739f34fd</t>
   </si>
   <si>
     <t xml:space="preserve">event_ts</t>
@@ -2596,16 +2601,16 @@
         <v>29</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="9" t="b">
         <v>0</v>
@@ -2614,7 +2619,7 @@
         <v>29</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>29</v>
@@ -2626,25 +2631,25 @@
         <v>29</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>29</v>
@@ -2662,18 +2667,18 @@
         <v>29</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>29</v>
@@ -2685,13 +2690,13 @@
         <v>29</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J3" s="9" t="b">
         <v>0</v>
@@ -2700,40 +2705,40 @@
         <v>29</v>
       </c>
       <c r="L3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="U3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="X3" s="7" t="n">
         <v>18</v>
@@ -2748,36 +2753,36 @@
         <v>29</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J4" s="9" t="b">
         <v>0</v>
@@ -2786,7 +2791,7 @@
         <v>29</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>29</v>
@@ -2798,7 +2803,7 @@
         <v>29</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>29</v>
@@ -2810,16 +2815,16 @@
         <v>29</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X4" s="7" t="n">
         <v>14</v>
@@ -2834,36 +2839,36 @@
         <v>29</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J5" s="9" t="b">
         <v>0</v>
@@ -2872,7 +2877,7 @@
         <v>29</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>29</v>
@@ -2884,7 +2889,7 @@
         <v>29</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="8" t="s">
         <v>29</v>
@@ -2896,16 +2901,16 @@
         <v>29</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="X5" s="7" t="n">
         <v>2</v>
@@ -2920,36 +2925,36 @@
         <v>29</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J6" s="9" t="b">
         <v>0</v>
@@ -2958,7 +2963,7 @@
         <v>29</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>29</v>
@@ -2970,7 +2975,7 @@
         <v>29</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q6" s="8" t="s">
         <v>29</v>
@@ -2982,16 +2987,16 @@
         <v>29</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="X6" s="7" t="n">
         <v>5</v>
@@ -3006,36 +3011,36 @@
         <v>29</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J7" s="9" t="b">
         <v>0</v>
@@ -3044,10 +3049,10 @@
         <v>29</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>29</v>
@@ -3056,7 +3061,7 @@
         <v>29</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>29</v>
@@ -3068,16 +3073,16 @@
         <v>29</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>3</v>
@@ -3092,18 +3097,18 @@
         <v>29</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>29</v>
@@ -3115,13 +3120,13 @@
         <v>29</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J8" s="9" t="b">
         <v>0</v>
@@ -3130,10 +3135,10 @@
         <v>29</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>29</v>
@@ -3142,7 +3147,7 @@
         <v>29</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="8" t="s">
         <v>29</v>
@@ -3154,16 +3159,16 @@
         <v>29</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X8" s="7" t="n">
         <v>10</v>
@@ -3178,18 +3183,18 @@
         <v>29</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>29</v>
@@ -3201,13 +3206,13 @@
         <v>29</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J9" s="9" t="b">
         <v>0</v>
@@ -3216,10 +3221,10 @@
         <v>29</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N9" s="8" t="s">
         <v>29</v>
@@ -3228,7 +3233,7 @@
         <v>29</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="8" t="s">
         <v>29</v>
@@ -3240,16 +3245,16 @@
         <v>29</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="V9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>8</v>
@@ -3264,36 +3269,36 @@
         <v>29</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9" t="b">
         <v>0</v>
@@ -3302,10 +3307,10 @@
         <v>29</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N10" s="8" t="s">
         <v>29</v>
@@ -3314,7 +3319,7 @@
         <v>29</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="8" t="s">
         <v>29</v>
@@ -3326,16 +3331,16 @@
         <v>29</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="V10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>3</v>
@@ -3350,18 +3355,18 @@
         <v>29</v>
       </c>
       <c r="AB10" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>29</v>
@@ -3373,13 +3378,13 @@
         <v>29</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J11" s="9" t="b">
         <v>0</v>
@@ -3388,10 +3393,10 @@
         <v>29</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>29</v>
@@ -3400,7 +3405,7 @@
         <v>29</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="8" t="s">
         <v>29</v>
@@ -3412,16 +3417,16 @@
         <v>29</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>7</v>
@@ -3436,18 +3441,18 @@
         <v>29</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>29</v>
@@ -3459,13 +3464,13 @@
         <v>29</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J12" s="9" t="b">
         <v>0</v>
@@ -3474,10 +3479,10 @@
         <v>29</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>29</v>
@@ -3486,31 +3491,31 @@
         <v>29</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X12" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="7" t="s">
         <v>29</v>
@@ -3522,18 +3527,18 @@
         <v>29</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>29</v>
@@ -3545,13 +3550,13 @@
         <v>29</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J13" s="9" t="b">
         <v>0</v>
@@ -3560,40 +3565,40 @@
         <v>29</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="U13" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="V13" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>23</v>
@@ -3608,18 +3613,18 @@
         <v>29</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>29</v>
@@ -3631,13 +3636,13 @@
         <v>29</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J14" s="9" t="b">
         <v>0</v>
@@ -3646,10 +3651,10 @@
         <v>29</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>29</v>
@@ -3658,7 +3663,7 @@
         <v>29</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="8" t="s">
         <v>29</v>
@@ -3670,16 +3675,16 @@
         <v>29</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V14" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X14" s="7" t="n">
         <v>4</v>
@@ -3694,18 +3699,18 @@
         <v>29</v>
       </c>
       <c r="AB14" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>29</v>
@@ -3717,13 +3722,13 @@
         <v>29</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J15" s="9" t="b">
         <v>0</v>
@@ -3732,10 +3737,10 @@
         <v>29</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>29</v>
@@ -3744,7 +3749,7 @@
         <v>29</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="8" t="s">
         <v>29</v>
@@ -3756,16 +3761,16 @@
         <v>29</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="V15" s="7" t="s">
         <v>29</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>2</v>
@@ -3780,7 +3785,7 @@
         <v>29</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
